--- a/data/trans_dic/P25C$productsfarma_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25C$productsfarma_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, por su cuenta, con parches, chicles u otros productos farmaceuticos</t>
+          <t>Población cuyo método para dejar de fumar fue, por su cuenta, con parches, chicles u otros productos farmaceuticos (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,29</t>
+          <t>0,69; 5,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 9,49</t>
+          <t>0,9; 10,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 5,14</t>
+          <t>1,23; 5,22</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 3,1</t>
+          <t>0,18; 3,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,48</t>
+          <t>1,56; 6,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,18</t>
+          <t>0,53; 3,21</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 17,27</t>
+          <t>4,98; 17,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,35</t>
+          <t>0,73; 6,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 11,27</t>
+          <t>3,71; 11,34</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,55</t>
+          <t>0,9; 4,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,02</t>
+          <t>1,76; 5,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,14</t>
+          <t>1,25; 4,26</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, por su cuenta, con parches, chicles u otros productos farmaceuticos</t>
+          <t>Población cuyo método para dejar de fumar fue, por su cuenta, con parches, chicles u otros productos farmaceuticos (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1432; 8773</t>
+          <t>1142; 8310</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>67; 4209</t>
+          <t>400; 4513</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2358; 10795</t>
+          <t>2591; 10956</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1003; 16875</t>
+          <t>984; 17537</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3165; 13158</t>
+          <t>3170; 13721</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3851; 23792</t>
+          <t>3966; 24026</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6791; 23721</t>
+          <t>6845; 23970</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>606; 5534</t>
+          <t>638; 5901</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8131; 25283</t>
+          <t>8323; 25456</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8005; 38542</t>
+          <t>7633; 40113</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5715; 16781</t>
+          <t>5891; 17747</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15990; 48987</t>
+          <t>14808; 50348</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$productsfarma_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25C$productsfarma_2023-Estudios-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,01</t>
+          <t>0,93; 5,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 10,18</t>
+          <t>0,87; 9,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,22</t>
+          <t>1,22; 5,37</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 3,22</t>
+          <t>0,71; 4,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,75</t>
+          <t>1,32; 5,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,21</t>
+          <t>1,38; 4,12</t>
         </is>
       </c>
     </row>
@@ -649,12 +649,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 17,45</t>
+          <t>5,1; 16,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,78</t>
+          <t>0,68; 6,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 11,34</t>
+          <t>3,88; 11,17</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,73</t>
+          <t>2,22; 5,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,3</t>
+          <t>1,75; 4,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,26</t>
+          <t>2,42; 4,95</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1564</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5795</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1142; 8310</t>
+          <t>1631; 10242</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>400; 4513</t>
+          <t>407; 4447</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2591; 10956</t>
+          <t>2719; 11977</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>6514</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>13227</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>984; 17537</t>
+          <t>2358; 13994</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3170; 13721</t>
+          <t>2927; 12825</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3966; 24026</t>
+          <t>7668; 22870</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12980</t>
+          <t>13684</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>16352</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6845; 23970</t>
+          <t>7584; 24814</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>638; 5901</t>
+          <t>652; 6244</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8323; 25456</t>
+          <t>9471; 27275</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>10944</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33651</t>
+          <t>35374</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7633; 40113</t>
+          <t>14560; 35762</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5891; 17747</t>
+          <t>6399; 17489</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14808; 50348</t>
+          <t>24776; 50643</t>
         </is>
       </c>
     </row>
